--- a/Result/checksun_type/店點開設管理.xlsx
+++ b/Result/checksun_type/店點開設管理.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>226.1</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>235.1</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>239.53</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>235.1</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>239.53</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>87560295.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>90409131.6</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>90409131.59999999</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>93926577.0</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>91142940.14</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>91142940.14</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-3023499.791926354</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>87560295</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>87560295.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>226.4</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>235.15</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>239.77</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>235.15</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>239.77</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>96574195.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>83666332.6</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>83666332.59999999</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>103194422.3</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>91481493.92</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>91481493.92</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-2766856.581867665</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>96574195</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>96574195.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>228.2</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>235.5</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>240.24</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>235.5</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>240.24</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>71644075.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>83897394.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>83897394</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>101865765.6</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>91508752.72</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>91508752.72</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-3267182.118145689</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>71644075</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>71644075.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>230.4</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>235.8</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>240.65</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>235.8</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>240.65</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>123805914.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>89321740.0</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>89321740</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>105919275.1</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>91810212.38</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>91810212.38</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-1194163.522894815</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>123805914</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>123805914.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>234.5</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>236.28</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>241.22</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>236.28</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>241.22</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>72461179.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>88104747.2</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>88104747.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>113492473.6</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>90562774.2</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>90562774.2</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-3778828.153861612</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>72461179</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>72461179.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>236.8</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>236.65</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>241.75</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>236.65</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>241.75</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>53846300.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>97444022.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>97444022.40000001</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>127286983.3</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>89517261.66</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>89517261.66</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-1835026.44260481</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>53846300</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>53846300.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>238.7</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>236.9</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>242.22</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>236.9</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>242.22</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>97729502.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>122722512.0</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>122722512</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>126605734.2</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>88915651.56</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>88915651.56</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>3001821.124997914</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>97729502</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>97729502.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>240.3</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>237.08</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>242.65</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>237.08</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>242.65</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>98765805.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>119834137.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>119834137.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>123032675.2</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>87410611.56</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>87410611.56</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>5102623.824251875</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>98765805</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>98765805.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>241.0</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>236.95</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>242.95</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>236.95</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>242.95</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>117720950.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>122516810.2</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>122516810.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>120087218.2</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>86170263.86</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>86170263.86</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>7810501.508034274</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>117720950</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>117720950.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>241.3</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>236.62</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>243.04</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>236.62</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>243.04</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>119157555.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>138880200.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>138880200</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>115721500.5</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>85084091.88</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>85084091.88</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>9369043.323865041</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>119157555</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>119157555.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>242.9</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>236.58</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>243.3</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>236.58</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>243.3</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>180238748.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>157129944.2</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>157129944.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>112511739.2</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>84766716.06</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>84766716.06</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>11107000.97777095</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>180238748</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>180238748.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>29.21</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>30.8</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>31.88</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>31.88</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>13046.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>11698.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>11698</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>17294.7</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>34387.42</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>34387.42</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-5549.003271599235</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>13046</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>13046.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>29.02</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>31.04</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>31.93</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>31.04</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>31.93</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>8093.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>11983.4</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>11983.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>18678.8</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>34584.5</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>34584.5</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-5952.775909733751</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>8093</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>8093.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>28.9</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>31.25</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>32.0</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>32</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>10897.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>14504.8</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>14504.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>21270.9</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>34565.74</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>34565.74</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-5786.316253149711</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>10897</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>10897.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>29.01</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>31.5</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>32.08</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>32.08</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>12050.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>18945.4</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>18945.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>25209.1</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>34557.06</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>34557.06</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-5642.291163274313</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>12050</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>12050.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>29.26</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>31.75</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>32.17</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>31.75</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>32.17</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>14404.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>20291.2</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>20291.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>26476.5</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>34460.38</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>34460.38</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-5358.566350478231</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>14404</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>14404.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>29.58</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>32.01</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>32.25</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>32.01</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>32.25</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>14473.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>22891.4</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>22891.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>26959.7</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>34296.58</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>34296.58</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-5014.082105395319</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>14473</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>14473.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>29.91</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>32.3</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>32.35</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>32.35</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>20700.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>25374.2</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>25374.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>28556.0</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>34314.24</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>34314.24</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-4350.280251512748</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>20700</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>20700.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>30.15</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>32.6</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>32.43</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>32.43</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>33100.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>28037.0</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>28037</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>32710.0</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>34047.14</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>34047.14</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-3913.803308412193</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>33100</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>33100.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>30.32</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>32.91</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>32.49</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>32.91</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>32.49</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>18779.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>31472.8</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>31472.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>38327.3</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>33558.52</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>33558.52</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-4479.057557253822</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>18779</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>18779.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>30.56</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>33.02</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>32.54</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>33.02</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>32.54</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>27405.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>32661.8</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>32661.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>42318.5</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>33657.96</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>33657.96</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-3592.204428554236</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>27405</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>27405.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>30.86</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>33.07</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>32.6</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>33.07</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>32.6</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>26887.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>31028.0</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>31028</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>43724.5</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>33550.22</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>33550.22</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-3121.192657963598</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>26887</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>26887.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>74.24</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>75.94</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>78.82</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>75.94</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>78.81999999999999</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>709.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>378.4</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>378.4</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>754.4</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>1063.24</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>1063.24</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-65.36342660409002</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>709</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>709.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>74.06</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>76.03</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>78.98</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>76.03</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>78.98</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>384.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>555.6</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>555.6</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>684.0</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>1078.44</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>1078.44</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-81.31309747373018</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>384</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>384.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>74.1</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>76.2</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>79.17</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>79.17</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>189.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>1003.4</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>1003.4</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>665.3</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>1085.84</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>1085.84</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-66.3728738062972</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>189</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>189.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>74.74</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>76.39</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>79.33</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>76.39</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>79.33</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>461.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>997.0</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>997</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>732.8</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>1111.82</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>1111.82</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-21.76638021688211</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>461</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>461.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>75.54</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>76.6</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>79.51</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>79.51000000000001</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>149.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>1109.8</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>1109.8</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>833.5</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>1227.54</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>1227.54</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>13.59169563288503</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>149</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>76.02000000000001</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>76.72</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>79.69</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>76.72</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>79.69</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>1595.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>1130.4</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>1130.4</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>970.4</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>1231.96</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>1231.96</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>97.04638628852092</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>1595</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>1595.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>76.67999999999999</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>76.82</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>79.87</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>76.81999999999999</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>79.87</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>2623.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>812.4</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>812.4</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>872.2</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>1215.96</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>1215.96</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>57.87285914341066</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>2623</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>2623.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>77.26000000000002</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>76.88</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>80.05</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>76.88</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>80.05</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>157.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>327.2</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>327.2</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>724.2</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>1165.2</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>1165.2</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-110.2990674618686</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>157</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>157.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>77.3</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>76.79</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>80.17</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>76.79000000000001</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>80.17</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>1025.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>468.6</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>468.6</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>767.1</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>1165.84</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>1165.84</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-82.39113877434352</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>1025</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>1025.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>77.14000000000001</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>76.71</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>80.29</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>76.70999999999999</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>80.29000000000001</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>252.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>557.2</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>557.2</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>750.8</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>1161.16</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>1161.16</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-132.5801285502242</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>252</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>77.0</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>76.63</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>80.44</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>76.63</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>80.44</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>5.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>810.4</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>810.4</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>743.3</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>1172.74</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>1172.74</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-116.7222522104029</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>5</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>69.14000000000001</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>70.18</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>71.13</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>70.18000000000001</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>71.13</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>154.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>0</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>0</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>17.28468721612921</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>154</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>154.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>69.7</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>70.34</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>71.18</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>70.34</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>71.18000000000001</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>0</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>0</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>41.2126055821771</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>0</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>69.82000000000001</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>70.53</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>71.21</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>70.53</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>71.20999999999999</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>436.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>0</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>0</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>41.2126055821771</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>436</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>436.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>69.94000000000001</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>70.72</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>71.26</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>70.72</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>71.26000000000001</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>527.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>0</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>0</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>36.77411383966177</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>527</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>527.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>70.46</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>71.03</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>71.35</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>71.03</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>71.34999999999999</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>511.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>0</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>0</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>19.37005014179482</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>511</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>511.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>70.74</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>71.28</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>71.42</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>71.28</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>71.42</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>14.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>0</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>0</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-4.470399788793543</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>14</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>14.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>70.72</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>71.35</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>71.45</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>71.34999999999999</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>71.45</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>0</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>0</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>22.6436498210679</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>0</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>70.7</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>71.5</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>71.43</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>71.43000000000001</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>179.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>257.0</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>257</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>207.0</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>0</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>22.6436498210679</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>179</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>179.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>70.68</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>71.63</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>71.37</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>71.63</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>71.37</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>905.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>236.4</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>236.4</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>195.6</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>0</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>34.43741684043724</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>905</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>905.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>70.28</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>71.78</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>71.61</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>71.78</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>71.61</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>133.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>58.0</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>58</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>124.8</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>0</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-27.72996659047934</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>133</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>69.86</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>71.88</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>71.86</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>71.88</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>71.86</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>48.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>93.8</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>93.8</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>143.1</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>0</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-32.8358726849859</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>48</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>48.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
